--- a/data/trans_orig/P05A03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>364107</t>
+          <t>363562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>397877</t>
+          <t>397828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>221377</t>
+          <t>222333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250731</t>
+          <t>251429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>595664</t>
+          <t>594274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>640248</t>
+          <t>639512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53887</t>
+          <t>52736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85366</t>
+          <t>84046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43403</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71384</t>
+          <t>70672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104586</t>
+          <t>104531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146571</t>
+          <t>147948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278511</t>
+          <t>276130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307605</t>
+          <t>307178</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287906</t>
+          <t>286362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317654</t>
+          <t>316126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>574866</t>
+          <t>575267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>618333</t>
+          <t>615411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,11%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46161</t>
+          <t>46957</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74945</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>40297</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67941</t>
+          <t>68089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92600</t>
+          <t>95007</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>131796</t>
+          <t>133385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33966</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>414628</t>
+          <t>416281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>452612</t>
+          <t>452992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130111</t>
+          <t>129008</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149381</t>
+          <t>149567</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>554404</t>
+          <t>555387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>596588</t>
+          <t>595788</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74513</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109490</t>
+          <t>109469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30166</t>
+          <t>30761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93029</t>
+          <t>92504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131385</t>
+          <t>129001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23489</t>
+          <t>24090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29747</t>
+          <t>29647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1008649</t>
+          <t>1007971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1059703</t>
+          <t>1057948</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>555353</t>
+          <t>555216</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>598138</t>
+          <t>596554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1576911</t>
+          <t>1576797</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1642853</t>
+          <t>1646280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142704</t>
+          <t>144107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190253</t>
+          <t>192639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>91158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126946</t>
+          <t>130304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244964</t>
+          <t>241946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>305219</t>
+          <t>306222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22445</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>44995</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>15811</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>42656</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70589</t>
+          <t>71501</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272661</t>
+          <t>270120</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301262</t>
+          <t>299686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>439037</t>
+          <t>438676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>477470</t>
+          <t>476653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>721868</t>
+          <t>722260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>767795</t>
+          <t>767329</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34757</t>
+          <t>36221</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60865</t>
+          <t>63297</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>73746</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107693</t>
+          <t>108997</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117795</t>
+          <t>117695</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160416</t>
+          <t>159019</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42186</t>
+          <t>39090</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234485</t>
+          <t>235715</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>261588</t>
+          <t>260420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1011427</t>
+          <t>1013074</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1065064</t>
+          <t>1064321</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1257081</t>
+          <t>1258862</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1314967</t>
+          <t>1315775</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30433</t>
+          <t>30992</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55299</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152632</t>
+          <t>153247</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>201483</t>
+          <t>202854</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>195424</t>
+          <t>193172</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>248826</t>
+          <t>246679</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24806</t>
+          <t>24648</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47022</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2635475</t>
+          <t>2635567</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2717855</t>
+          <t>2722000</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2707986</t>
+          <t>2705795</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2800378</t>
+          <t>2800074</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5373334</t>
+          <t>5377326</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5493385</t>
+          <t>5502041</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>437606</t>
+          <t>434375</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>516052</t>
+          <t>515328</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>461570</t>
+          <t>465277</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>548108</t>
+          <t>550795</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>923334</t>
+          <t>920196</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1042068</t>
+          <t>1040602</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71447</t>
+          <t>70886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110418</t>
+          <t>110679</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>80680</t>
+          <t>81031</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>121411</t>
+          <t>120532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>159848</t>
+          <t>162425</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>215091</t>
+          <t>213966</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>368346</t>
+          <t>370577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>398281</t>
+          <t>397215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251466</t>
+          <t>251512</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>277186</t>
+          <t>278551</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>631054</t>
+          <t>631343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>668783</t>
+          <t>669952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28620</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54204</t>
+          <t>53948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46591</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58060</t>
+          <t>55455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92031</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>19260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>29235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331245</t>
+          <t>331673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364102</t>
+          <t>363603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>276025</t>
+          <t>276304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300782</t>
+          <t>301832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617498</t>
+          <t>617117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656721</t>
+          <t>657221</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39754</t>
+          <t>38928</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69235</t>
+          <t>67428</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28090</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51950</t>
+          <t>51857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>76899</t>
+          <t>73979</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111142</t>
+          <t>112153</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22807</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29459</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>527783</t>
+          <t>528043</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>560876</t>
+          <t>561807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>215718</t>
+          <t>214107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>236313</t>
+          <t>236810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>752765</t>
+          <t>751566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>792702</t>
+          <t>792308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50218</t>
+          <t>49374</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81347</t>
+          <t>81250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69519</t>
+          <t>69780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106671</t>
+          <t>106942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22201</t>
+          <t>22433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,82 +5312,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4898</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>18950</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>29589</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4898</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14259</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>18950</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>11273</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>29572</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>999622</t>
+          <t>999401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1043851</t>
+          <t>1046236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624129</t>
+          <t>625454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>665718</t>
+          <t>667179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1639008</t>
+          <t>1640743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1700094</t>
+          <t>1704161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80950</t>
+          <t>79436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>120800</t>
+          <t>118458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74123</t>
+          <t>73712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112820</t>
+          <t>111389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165354</t>
+          <t>162285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>218015</t>
+          <t>218864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44251</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>32968</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37712</t>
+          <t>37757</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>69473</t>
+          <t>68657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>436289</t>
+          <t>437528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>464534</t>
+          <t>464171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>654505</t>
+          <t>654982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>690180</t>
+          <t>689528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1105105</t>
+          <t>1101876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1146968</t>
+          <t>1144572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>35430</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61857</t>
+          <t>60690</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53500</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86659</t>
+          <t>86237</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>95295</t>
+          <t>96206</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135500</t>
+          <t>137783</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28846</t>
+          <t>29272</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>213983</t>
+          <t>214328</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237358</t>
+          <t>237253</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>933483</t>
+          <t>934706</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>980002</t>
+          <t>979984</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1159034</t>
+          <t>1160078</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1209947</t>
+          <t>1209430</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44098</t>
+          <t>44242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92193</t>
+          <t>92410</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134253</t>
+          <t>133274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>120132</t>
+          <t>122509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>167982</t>
+          <t>166352</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36152</t>
+          <t>37198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41053</t>
+          <t>43092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2938884</t>
+          <t>2941865</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3019473</t>
+          <t>3017885</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3018538</t>
+          <t>3019036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3102567</t>
+          <t>3100269</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5976688</t>
+          <t>5984239</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6098386</t>
+          <t>6096648</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>299799</t>
+          <t>299292</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>371718</t>
+          <t>373787</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>327604</t>
+          <t>333431</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>406037</t>
+          <t>406272</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>652106</t>
+          <t>650858</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>758425</t>
+          <t>757576</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63066</t>
+          <t>62286</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>101758</t>
+          <t>100020</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,82 +7136,82 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>73704</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>57888</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>94060</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>153357</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>128560</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>179348</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>73704</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>57018</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>92743</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>153357</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>128905</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>183246</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016 (tasa de respuesta: 99,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>337049</t>
+          <t>335510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369579</t>
+          <t>369512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267702</t>
+          <t>267787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297640</t>
+          <t>297072</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>614252</t>
+          <t>613167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>660189</t>
+          <t>657833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40526</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69610</t>
+          <t>72409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>33656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60789</t>
+          <t>60154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80408</t>
+          <t>83752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122786</t>
+          <t>123133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41020</t>
+          <t>41247</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298026</t>
+          <t>298352</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>328259</t>
+          <t>328685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281175</t>
+          <t>281114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314573</t>
+          <t>312837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>592574</t>
+          <t>591503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>635005</t>
+          <t>634116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39590</t>
+          <t>38947</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68571</t>
+          <t>66960</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45281</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76272</t>
+          <t>76233</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92574</t>
+          <t>92893</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>132864</t>
+          <t>132853</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>20128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>28698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>421481</t>
+          <t>422131</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>455215</t>
+          <t>453325</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>139173</t>
+          <t>138444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155784</t>
+          <t>155525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>569205</t>
+          <t>567307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>605054</t>
+          <t>605214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>47726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78834</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26950</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64099</t>
+          <t>63907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98385</t>
+          <t>96998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25771</t>
+          <t>24383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24972</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>918398</t>
+          <t>918095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>970706</t>
+          <t>968240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>664438</t>
+          <t>665501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>706989</t>
+          <t>707897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1602188</t>
+          <t>1593276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1666680</t>
+          <t>1661032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123743</t>
+          <t>124499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168374</t>
+          <t>168762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>75792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111883</t>
+          <t>110469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207250</t>
+          <t>209680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265414</t>
+          <t>266564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69583</t>
+          <t>70092</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51815</t>
+          <t>51134</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74419</t>
+          <t>71807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114117</t>
+          <t>112704</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>527386</t>
+          <t>527709</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>560924</t>
+          <t>560897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>618118</t>
+          <t>618903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>656442</t>
+          <t>656066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1156261</t>
+          <t>1158193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1206286</t>
+          <t>1207720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>44307</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74378</t>
+          <t>74318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>53187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85428</t>
+          <t>85224</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>105105</t>
+          <t>105364</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>148854</t>
+          <t>149202</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22403</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36364</t>
+          <t>35447</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50682</t>
+          <t>50950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>235710</t>
+          <t>235179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>259072</t>
+          <t>257801</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>850449</t>
+          <t>851174</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>901116</t>
+          <t>903096</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1092231</t>
+          <t>1095276</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1151963</t>
+          <t>1152861</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42725</t>
+          <t>42909</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127231</t>
+          <t>125446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173249</t>
+          <t>171788</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155459</t>
+          <t>154397</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>210397</t>
+          <t>208275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37643</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67775</t>
+          <t>65315</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>41177</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69916</t>
+          <t>69371</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2800242</t>
+          <t>2803385</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2889988</t>
+          <t>2889985</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2885580</t>
+          <t>2886872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2978823</t>
+          <t>2974881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5718396</t>
+          <t>5716818</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5838719</t>
+          <t>5845650</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>363519</t>
+          <t>365329</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>444527</t>
+          <t>441228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>391594</t>
+          <t>398705</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>473947</t>
+          <t>477833</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>781558</t>
+          <t>780110</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>895579</t>
+          <t>896196</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90699</t>
+          <t>89662</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>130866</t>
+          <t>133279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112909</t>
+          <t>113912</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160630</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>210460</t>
+          <t>213223</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>273975</t>
+          <t>278069</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>432414</t>
+          <t>431615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>462974</t>
+          <t>461950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>385790</t>
+          <t>385855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>407101</t>
+          <t>405972</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>827170</t>
+          <t>826563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>862515</t>
+          <t>860886</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27780</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52425</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48620</t>
+          <t>49161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62408</t>
+          <t>63672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>94657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25771</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34367</t>
+          <t>34785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>394473</t>
+          <t>395840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418667</t>
+          <t>419761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>323590</t>
+          <t>323444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344999</t>
+          <t>343533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724579</t>
+          <t>724553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>758053</t>
+          <t>758211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27403</t>
+          <t>26375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50004</t>
+          <t>49096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24554</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>41563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>55656</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84604</t>
+          <t>86199</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26584</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>591933</t>
+          <t>591140</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>652116</t>
+          <t>650136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138297</t>
+          <t>138084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153718</t>
+          <t>153673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>736912</t>
+          <t>735901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>810421</t>
+          <t>807647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57352</t>
+          <t>57941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23674</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74760</t>
+          <t>76379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>936759</t>
+          <t>938126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>973894</t>
+          <t>971994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>880163</t>
+          <t>878097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>942847</t>
+          <t>938387</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1833155</t>
+          <t>1832117</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1905082</t>
+          <t>1904986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>49374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82529</t>
+          <t>82462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71755</t>
+          <t>74092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80114</t>
+          <t>80722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142907</t>
+          <t>142152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20503</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40826</t>
+          <t>41333</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>418097</t>
+          <t>416651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>444326</t>
+          <t>443465</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>739742</t>
+          <t>739930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>780350</t>
+          <t>778386</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1169361</t>
+          <t>1167613</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1214452</t>
+          <t>1212440</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44702</t>
+          <t>45946</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>45925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79842</t>
+          <t>79724</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73550</t>
+          <t>74927</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>115093</t>
+          <t>114961</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20710</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>34397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>199832</t>
+          <t>202037</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>230197</t>
+          <t>230907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>686647</t>
+          <t>683613</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>714223</t>
+          <t>712914</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>898000</t>
+          <t>897944</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>937579</t>
+          <t>937931</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21549</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>34983</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57549</t>
+          <t>59022</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40538</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>70965</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27863</t>
+          <t>27732</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23217</t>
+          <t>25006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41703</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3048010</t>
+          <t>3047265</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3152988</t>
+          <t>3149363</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3205183</t>
+          <t>3204635</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3297660</t>
+          <t>3305975</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6271355</t>
+          <t>6272545</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6408393</t>
+          <t>6415292</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>167204</t>
+          <t>160955</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>250510</t>
+          <t>248458</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>198061</t>
+          <t>194250</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>277300</t>
+          <t>278690</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>393954</t>
+          <t>395273</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>508197</t>
+          <t>508363</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44432</t>
+          <t>44452</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85626</t>
+          <t>84353</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53850</t>
+          <t>53839</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86344</t>
+          <t>87123</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>106532</t>
+          <t>105296</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>159918</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>363562</t>
+          <t>362723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>397828</t>
+          <t>396924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222333</t>
+          <t>220410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251429</t>
+          <t>251460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>594274</t>
+          <t>594669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>639512</t>
+          <t>639530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52736</t>
+          <t>54019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84046</t>
+          <t>86162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43842</t>
+          <t>43339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70672</t>
+          <t>72264</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104531</t>
+          <t>105119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147948</t>
+          <t>147329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>40091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276130</t>
+          <t>276796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307178</t>
+          <t>307335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286362</t>
+          <t>288940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316126</t>
+          <t>317547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>575267</t>
+          <t>574543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>615411</t>
+          <t>617166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46957</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>76101</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40297</t>
+          <t>40011</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68089</t>
+          <t>66545</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95007</t>
+          <t>94451</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133385</t>
+          <t>133005</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32989</t>
+          <t>34626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>416281</t>
+          <t>416472</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>452992</t>
+          <t>453950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>129008</t>
+          <t>130450</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149567</t>
+          <t>149590</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>555387</t>
+          <t>555285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>595788</t>
+          <t>598054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74345</t>
+          <t>75435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109469</t>
+          <t>110088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30761</t>
+          <t>29602</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92504</t>
+          <t>91084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129001</t>
+          <t>131347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1007971</t>
+          <t>1007830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1057948</t>
+          <t>1059196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>555216</t>
+          <t>554609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>596554</t>
+          <t>597011</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1576797</t>
+          <t>1574270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1646280</t>
+          <t>1640554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144107</t>
+          <t>143863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192639</t>
+          <t>193006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91158</t>
+          <t>89521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130304</t>
+          <t>129305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241946</t>
+          <t>245755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306222</t>
+          <t>308416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22706</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>15993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>35541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42656</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71501</t>
+          <t>72003</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270120</t>
+          <t>271452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>299686</t>
+          <t>299602</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>438676</t>
+          <t>440096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>476653</t>
+          <t>478475</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>722260</t>
+          <t>722734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>767329</t>
+          <t>769582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36221</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63297</t>
+          <t>63087</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>72214</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108997</t>
+          <t>108153</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117695</t>
+          <t>115985</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>159019</t>
+          <t>161661</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25521</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39090</t>
+          <t>40199</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>235715</t>
+          <t>233437</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>260420</t>
+          <t>258981</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1013074</t>
+          <t>1011399</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1064321</t>
+          <t>1065424</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,47 +3063,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>1287412</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1257831</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1317093</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>81,59%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>85,43%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1287412</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1258862</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1315775</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>83,5%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>81,65%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54402</t>
+          <t>56318</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153247</t>
+          <t>152012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>202854</t>
+          <t>202643</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>193172</t>
+          <t>190871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>246679</t>
+          <t>247717</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42105</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24648</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48919</t>
+          <t>48551</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2635567</t>
+          <t>2636624</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2722000</t>
+          <t>2722309</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2705795</t>
+          <t>2711580</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2800074</t>
+          <t>2800749</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5377326</t>
+          <t>5369347</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5502041</t>
+          <t>5494676</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>434375</t>
+          <t>434359</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>515328</t>
+          <t>514258</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>465277</t>
+          <t>464833</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>550795</t>
+          <t>545848</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>920196</t>
+          <t>925703</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1040602</t>
+          <t>1038808</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70886</t>
+          <t>73417</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110679</t>
+          <t>112180</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>81031</t>
+          <t>79979</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>120532</t>
+          <t>119626</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>162425</t>
+          <t>162535</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>213966</t>
+          <t>217422</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>370577</t>
+          <t>369658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>397215</t>
+          <t>397058</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251512</t>
+          <t>250856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>278551</t>
+          <t>277713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>631343</t>
+          <t>629524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>669952</t>
+          <t>667824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>29685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53948</t>
+          <t>54752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55455</t>
+          <t>57053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92285</t>
+          <t>90879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19260</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29235</t>
+          <t>30429</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331673</t>
+          <t>330643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363603</t>
+          <t>363276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,82 +4630,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>88,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>289900</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>276444</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>301410</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>90,42%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>638639</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>616611</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>657321</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>85,61%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>82,66%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>88,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>289900</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>276304</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>301832</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,97%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>82,89%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>638639</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>617117</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>657221</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>85,61%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>82,73%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38928</t>
+          <t>38391</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67428</t>
+          <t>70591</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51857</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73979</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112153</t>
+          <t>111950</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>27658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>528043</t>
+          <t>527501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>561807</t>
+          <t>561203</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>214107</t>
+          <t>214396</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>236810</t>
+          <t>235595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>751566</t>
+          <t>752145</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>792308</t>
+          <t>793061</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49374</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81250</t>
+          <t>81531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>34568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69780</t>
+          <t>69374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106942</t>
+          <t>105156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22433</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29589</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>999401</t>
+          <t>999422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1046236</t>
+          <t>1044147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>625454</t>
+          <t>624004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>667179</t>
+          <t>666415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1640743</t>
+          <t>1637162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1704161</t>
+          <t>1699990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79436</t>
+          <t>79214</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118458</t>
+          <t>119847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73712</t>
+          <t>73748</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111389</t>
+          <t>111866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162285</t>
+          <t>162422</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>218864</t>
+          <t>219622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43605</t>
+          <t>44821</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32968</t>
+          <t>33351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37757</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68657</t>
+          <t>68298</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>437528</t>
+          <t>437310</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>464171</t>
+          <t>464110</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>654982</t>
+          <t>656010</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>689528</t>
+          <t>691316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1101876</t>
+          <t>1104876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1144572</t>
+          <t>1146085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>34935</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60690</t>
+          <t>61257</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>51405</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86237</t>
+          <t>84117</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96206</t>
+          <t>95854</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137783</t>
+          <t>135869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>29217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214328</t>
+          <t>214478</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237253</t>
+          <t>236619</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>934706</t>
+          <t>934977</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>979984</t>
+          <t>977959</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1160078</t>
+          <t>1157965</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1209430</t>
+          <t>1210316</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44242</t>
+          <t>43890</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92410</t>
+          <t>92688</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>133274</t>
+          <t>134908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>122509</t>
+          <t>119818</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>166352</t>
+          <t>169777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37198</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>19871</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43092</t>
+          <t>41398</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2941865</t>
+          <t>2936751</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3017885</t>
+          <t>3019681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3019036</t>
+          <t>3017997</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3100269</t>
+          <t>3105456</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5984239</t>
+          <t>5985321</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6096648</t>
+          <t>6102538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>299292</t>
+          <t>302540</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>373787</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>333431</t>
+          <t>326576</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>406272</t>
+          <t>406769</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>650858</t>
+          <t>649790</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>757576</t>
+          <t>755077</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62286</t>
+          <t>62653</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100020</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>57841</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94060</t>
+          <t>95263</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>128560</t>
+          <t>128206</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>179348</t>
+          <t>178259</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>335510</t>
+          <t>336487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369512</t>
+          <t>369339</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267787</t>
+          <t>268267</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297072</t>
+          <t>297207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>613167</t>
+          <t>616207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>657833</t>
+          <t>657938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>41029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72409</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33656</t>
+          <t>32836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60154</t>
+          <t>59766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83752</t>
+          <t>81881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123133</t>
+          <t>120188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>26449</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41247</t>
+          <t>40330</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298352</t>
+          <t>298594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>328685</t>
+          <t>329442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281114</t>
+          <t>281592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312837</t>
+          <t>312211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>591503</t>
+          <t>591180</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>634116</t>
+          <t>633782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38947</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66960</t>
+          <t>67179</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>48527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76233</t>
+          <t>76292</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92893</t>
+          <t>94509</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>132853</t>
+          <t>133292</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>27965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>422131</t>
+          <t>423104</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>453325</t>
+          <t>452696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138444</t>
+          <t>139121</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155525</t>
+          <t>155373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>567307</t>
+          <t>568010</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>605214</t>
+          <t>604133</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47726</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76903</t>
+          <t>76662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63907</t>
+          <t>64767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96998</t>
+          <t>98644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24383</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24654</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>918095</t>
+          <t>917350</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>968240</t>
+          <t>967234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>665501</t>
+          <t>665591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>707897</t>
+          <t>707441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1593276</t>
+          <t>1596522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1661032</t>
+          <t>1663790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124499</t>
+          <t>123621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168762</t>
+          <t>169076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75792</t>
+          <t>76668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110469</t>
+          <t>112124</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209680</t>
+          <t>211154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266564</t>
+          <t>269854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>41749</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70092</t>
+          <t>71299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>26174</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51134</t>
+          <t>49739</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71807</t>
+          <t>74877</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112704</t>
+          <t>110579</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>527709</t>
+          <t>528347</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>560897</t>
+          <t>560302</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>618903</t>
+          <t>618863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>656066</t>
+          <t>654179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1158193</t>
+          <t>1158095</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1207720</t>
+          <t>1207751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44307</t>
+          <t>44350</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74318</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53187</t>
+          <t>54280</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85224</t>
+          <t>84603</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>105364</t>
+          <t>105447</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>149202</t>
+          <t>150059</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35447</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50950</t>
+          <t>51917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>235179</t>
+          <t>236569</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>257801</t>
+          <t>258521</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>851174</t>
+          <t>852366</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>903096</t>
+          <t>902524</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1095276</t>
+          <t>1097326</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1152861</t>
+          <t>1154997</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42909</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125446</t>
+          <t>126158</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>171788</t>
+          <t>172353</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154397</t>
+          <t>153243</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>208275</t>
+          <t>206892</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37145</t>
+          <t>37461</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65315</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41177</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69371</t>
+          <t>71594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2803385</t>
+          <t>2797468</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2889985</t>
+          <t>2883805</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2886872</t>
+          <t>2890134</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2974881</t>
+          <t>2978795</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5716818</t>
+          <t>5714702</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5845650</t>
+          <t>5842663</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,18%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>365329</t>
+          <t>367921</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>441228</t>
+          <t>446491</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>398705</t>
+          <t>394621</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>477833</t>
+          <t>473913</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,47 +10484,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>836186</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>781241</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>890580</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>12,19%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>11,39%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>836186</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>780110</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>896196</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89662</t>
+          <t>88523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>133279</t>
+          <t>131292</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>113912</t>
+          <t>113373</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>158855</t>
+          <t>157834</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>213223</t>
+          <t>214271</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>278069</t>
+          <t>278891</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>448482</t>
+          <t>488779</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>431615</t>
+          <t>471698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>461950</t>
+          <t>502912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>396654</t>
+          <t>431174</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>385855</t>
+          <t>418485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>405972</t>
+          <t>441617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,17 +11076,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>845137</t>
+          <t>919953</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>826563</t>
+          <t>899670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>860886</t>
+          <t>937315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39279</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>31572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54145</t>
+          <t>60595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>41374</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29699</t>
+          <t>32623</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49161</t>
+          <t>52766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>77553</t>
+          <t>85146</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63672</t>
+          <t>70238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94657</t>
+          <t>102872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25806</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,27 +11302,27 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34785</t>
+          <t>37892</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>502050</t>
+          <t>547392</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>502050</t>
+          <t>547392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>502050</t>
+          <t>547392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>444195</t>
+          <t>482719</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>444195</t>
+          <t>482719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444195</t>
+          <t>482719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>946245</t>
+          <t>1030111</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>946245</t>
+          <t>1030111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>946245</t>
+          <t>1030111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>408932</t>
+          <t>435277</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395840</t>
+          <t>421581</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419761</t>
+          <t>447554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>334382</t>
+          <t>369602</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>323444</t>
+          <t>358157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>380384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>743314</t>
+          <t>804880</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724553</t>
+          <t>785044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>758211</t>
+          <t>819061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36497</t>
+          <t>40818</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26375</t>
+          <t>28941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49096</t>
+          <t>54845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41563</t>
+          <t>45377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>76366</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55656</t>
+          <t>62540</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>92821</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>451025</t>
+          <t>481929</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451025</t>
+          <t>481929</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451025</t>
+          <t>481929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>378587</t>
+          <t>418054</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>378587</t>
+          <t>418054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>378587</t>
+          <t>418054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>829612</t>
+          <t>899984</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>829612</t>
+          <t>899984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>829612</t>
+          <t>899984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>622394</t>
+          <t>416417</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>591140</t>
+          <t>400659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>650136</t>
+          <t>429532</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>147262</t>
+          <t>166104</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138084</t>
+          <t>155554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153673</t>
+          <t>173408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>769656</t>
+          <t>582520</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>735901</t>
+          <t>564322</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>807647</t>
+          <t>597434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>41481</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>29846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>56375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24109</t>
+          <t>26136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>57702</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>43584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76379</t>
+          <t>74128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>665785</t>
+          <t>469245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>665785</t>
+          <t>469245</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>665785</t>
+          <t>469245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166449</t>
+          <t>187011</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166449</t>
+          <t>187011</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166449</t>
+          <t>187011</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>832234</t>
+          <t>656255</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>832234</t>
+          <t>656255</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>832234</t>
+          <t>656255</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>956251</t>
+          <t>1039813</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>938126</t>
+          <t>1017802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>971994</t>
+          <t>1057118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>905062</t>
+          <t>778599</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>878097</t>
+          <t>762538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>938387</t>
+          <t>793703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1861313</t>
+          <t>1818412</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1832117</t>
+          <t>1795024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1904986</t>
+          <t>1844102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63368</t>
+          <t>73382</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49374</t>
+          <t>56992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82462</t>
+          <t>93431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52417</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>45833</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74092</t>
+          <t>73309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>115786</t>
+          <t>132867</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80722</t>
+          <t>111196</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142152</t>
+          <t>156733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>24816</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27256</t>
+          <t>29188</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41333</t>
+          <t>44616</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1031090</t>
+          <t>1127118</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1031090</t>
+          <t>1127118</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1031090</t>
+          <t>1127118</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>974754</t>
+          <t>857602</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>974754</t>
+          <t>857602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>974754</t>
+          <t>857602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2005844</t>
+          <t>1984720</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2005844</t>
+          <t>1984720</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2005844</t>
+          <t>1984720</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>432306</t>
+          <t>523205</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>416651</t>
+          <t>509147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>443465</t>
+          <t>536656</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>758208</t>
+          <t>737828</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>739930</t>
+          <t>722491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>778386</t>
+          <t>751987</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1190513</t>
+          <t>1261033</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1167613</t>
+          <t>1241162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1212440</t>
+          <t>1280388</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31377</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>21899</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>46410</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62795</t>
+          <t>69819</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45925</t>
+          <t>56900</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79724</t>
+          <t>84231</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>94172</t>
+          <t>102603</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74927</t>
+          <t>85155</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>114961</t>
+          <t>120551</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>20699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>23028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34397</t>
+          <t>36748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>834385</t>
+          <t>823318</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>834385</t>
+          <t>823318</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>834385</t>
+          <t>823318</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1308433</t>
+          <t>1390294</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1308433</t>
+          <t>1390294</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1308433</t>
+          <t>1390294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>219293</t>
+          <t>216778</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202037</t>
+          <t>201144</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>230907</t>
+          <t>227543</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>700835</t>
+          <t>775329</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>683613</t>
+          <t>756257</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>712914</t>
+          <t>789296</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>920128</t>
+          <t>992106</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>897944</t>
+          <t>969861</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>937931</t>
+          <t>1011884</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44305</t>
+          <t>51639</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>39517</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59022</t>
+          <t>68505</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>53851</t>
+          <t>61845</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40821</t>
+          <t>45111</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70965</t>
+          <t>80252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27732</t>
+          <t>24972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25006</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>757888</t>
+          <t>840479</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>757888</t>
+          <t>840479</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>757888</t>
+          <t>840479</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>997319</t>
+          <t>1076609</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>997319</t>
+          <t>1076609</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>997319</t>
+          <t>1076609</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3087657</t>
+          <t>3120269</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3047265</t>
+          <t>3083683</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3149363</t>
+          <t>3157150</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3242403</t>
+          <t>3258635</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3204635</t>
+          <t>3228840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3305975</t>
+          <t>3292467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6330060</t>
+          <t>6378904</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6272545</t>
+          <t>6328070</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6415292</t>
+          <t>6429730</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>213659</t>
+          <t>242444</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>160955</t>
+          <t>209869</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>248458</t>
+          <t>276449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>244875</t>
+          <t>274085</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>194250</t>
+          <t>244304</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>278690</t>
+          <t>304128</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>458535</t>
+          <t>516529</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>395273</t>
+          <t>475773</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>508363</t>
+          <t>567395</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>62112</t>
+          <t>66078</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>49892</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84353</t>
+          <t>87872</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>68980</t>
+          <t>76462</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>61188</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>91912</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>131092</t>
+          <t>142540</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>105296</t>
+          <t>120088</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>168472</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3363429</t>
+          <t>3428790</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3363429</t>
+          <t>3428790</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3363429</t>
+          <t>3428790</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3556258</t>
+          <t>3609183</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3556258</t>
+          <t>3609183</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3556258</t>
+          <t>3609183</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6919687</t>
+          <t>7037973</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6919687</t>
+          <t>7037973</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6919687</t>
+          <t>7037973</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
